--- a/Data/EXCEL/Transfer/salemon/202208/8171-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8171-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07E7E357-E2DA-43DF-8A49-0BC1CF6001A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3192FBE7-5C44-4E92-B02C-C6798437B7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8171-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,23 +1227,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q148"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="5" width="9.375" customWidth="1"/>
-    <col min="6" max="6" width="8.875" customWidth="1"/>
-    <col min="7" max="7" width="10.375" customWidth="1"/>
-    <col min="8" max="8" width="10.875" customWidth="1"/>
-    <col min="9" max="9" width="9.375" customWidth="1"/>
-    <col min="10" max="11" width="10.875" customWidth="1"/>
-    <col min="12" max="12" width="9.375" customWidth="1"/>
-    <col min="13" max="13" width="10.875" customWidth="1"/>
-    <col min="14" max="14" width="9.375" customWidth="1"/>
-    <col min="15" max="16" width="10.875" customWidth="1"/>
-    <col min="17" max="17" width="10.75" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="5" width="13.125" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="13.125" customWidth="1"/>
+    <col min="10" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="13.125" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="13.125" customWidth="1"/>
+    <col min="15" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1262,7 +1270,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1301,7 +1309,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1344,7 +1352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1383,7 +1391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1436,7 +1444,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1489,7 +1497,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1542,7 +1550,7 @@
         <v>107.6</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1595,7 +1603,7 @@
         <v>248.9</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1648,7 +1656,7 @@
         <v>221.2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1701,7 +1709,7 @@
         <v>352.6</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1754,7 +1762,7 @@
         <v>110.9</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1807,7 +1815,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1860,7 +1868,7 @@
         <v>267.3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1913,7 +1921,7 @@
         <v>263.8</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1966,7 +1974,7 @@
         <v>221.4</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2019,7 +2027,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2072,7 +2080,7 @@
         <v>265.3</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2125,7 +2133,7 @@
         <v>231.1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2178,7 +2186,7 @@
         <v>173.9</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2231,7 +2239,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2284,7 +2292,7 @@
         <v>80.599999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2337,7 +2345,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2390,7 +2398,7 @@
         <v>117.6</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2443,7 +2451,7 @@
         <v>134.4</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2496,7 +2504,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2549,7 +2557,7 @@
         <v>60.9</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2602,7 +2610,7 @@
         <v>63.7</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2655,7 +2663,7 @@
         <v>72.400000000000006</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2708,7 +2716,7 @@
         <v>69.3</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2761,7 +2769,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2814,7 +2822,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2867,7 +2875,7 @@
         <v>128.4</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2920,7 +2928,7 @@
         <v>271.39999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2973,7 +2981,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3026,7 +3034,7 @@
         <v>101.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3079,7 +3087,7 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3132,7 +3140,7 @@
         <v>-59.6</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3185,7 +3193,7 @@
         <v>-62.2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3238,7 +3246,7 @@
         <v>-63.3</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3291,7 +3299,7 @@
         <v>-66.3</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3344,7 +3352,7 @@
         <v>-67.900000000000006</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3397,7 +3405,7 @@
         <v>-71.3</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3450,7 +3458,7 @@
         <v>-76.400000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3503,7 +3511,7 @@
         <v>-77.3</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3556,7 +3564,7 @@
         <v>-84.3</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3609,7 +3617,7 @@
         <v>-85.5</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3662,7 +3670,7 @@
         <v>-81.3</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3715,7 +3723,7 @@
         <v>-73.900000000000006</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3768,7 +3776,7 @@
         <v>-52.9</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3821,7 +3829,7 @@
         <v>-53.1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3874,7 +3882,7 @@
         <v>-55.1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3927,7 +3935,7 @@
         <v>-57.3</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3980,7 +3988,7 @@
         <v>-60.6</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4033,7 +4041,7 @@
         <v>-61.2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4086,7 +4094,7 @@
         <v>-61.2</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4139,7 +4147,7 @@
         <v>-65.7</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4192,7 +4200,7 @@
         <v>-72.599999999999994</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4245,7 +4253,7 @@
         <v>-75.2</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4298,7 +4306,7 @@
         <v>-77.099999999999994</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4351,7 +4359,7 @@
         <v>-78.8</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4404,7 +4412,7 @@
         <v>-48.5</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4457,7 +4465,7 @@
         <v>-47.1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4510,7 +4518,7 @@
         <v>-43.4</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4563,7 +4571,7 @@
         <v>-41.2</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4616,7 +4624,7 @@
         <v>-37.4</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4669,7 +4677,7 @@
         <v>-32.799999999999997</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4722,7 +4730,7 @@
         <v>-22.1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4775,7 +4783,7 @@
         <v>-14.8</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4828,7 +4836,7 @@
         <v>-8.08</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4881,7 +4889,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4934,7 +4942,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4987,7 +4995,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5040,7 +5048,7 @@
         <v>-24.4</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5093,7 +5101,7 @@
         <v>-24.4</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5146,7 +5154,7 @@
         <v>-27</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5199,7 +5207,7 @@
         <v>-24</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5252,7 +5260,7 @@
         <v>-22.1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5305,7 +5313,7 @@
         <v>-24.1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5358,7 +5366,7 @@
         <v>-31.8</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5411,7 +5419,7 @@
         <v>-32.9</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5464,7 +5472,7 @@
         <v>-27.7</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5517,7 +5525,7 @@
         <v>-20.3</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5570,7 +5578,7 @@
         <v>-5.04</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5623,7 +5631,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5676,7 +5684,7 @@
         <v>-31.4</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5729,7 +5737,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5782,7 +5790,7 @@
         <v>-28.8</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5835,7 +5843,7 @@
         <v>-29.8</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5888,7 +5896,7 @@
         <v>-31.6</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5941,7 +5949,7 @@
         <v>-34</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5994,7 +6002,7 @@
         <v>-37.6</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6047,7 +6055,7 @@
         <v>-40.6</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6100,7 +6108,7 @@
         <v>-39</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6153,7 +6161,7 @@
         <v>-26.5</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6206,7 +6214,7 @@
         <v>-6.56</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6259,7 +6267,7 @@
         <v>-30.2</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6312,7 +6320,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6365,7 +6373,7 @@
         <v>161.1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6418,7 +6426,7 @@
         <v>165.5</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6471,7 +6479,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6524,7 +6532,7 @@
         <v>178.5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6577,7 +6585,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6630,7 +6638,7 @@
         <v>209.6</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6683,7 +6691,7 @@
         <v>219.5</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6736,7 +6744,7 @@
         <v>185.3</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6789,7 +6797,7 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6842,7 +6850,7 @@
         <v>74.599999999999994</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6895,7 +6903,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6948,7 +6956,7 @@
         <v>-35.200000000000003</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -7001,7 +7009,7 @@
         <v>-35.6</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7054,7 +7062,7 @@
         <v>-33.299999999999997</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7107,7 +7115,7 @@
         <v>-32.1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7160,7 +7168,7 @@
         <v>-30.8</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7213,7 +7221,7 @@
         <v>-30.7</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7266,7 +7274,7 @@
         <v>-23.8</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7319,7 +7327,7 @@
         <v>-24</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7372,7 +7380,7 @@
         <v>-9.2799999999999994</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7425,7 +7433,7 @@
         <v>-0.33</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7478,7 +7486,7 @@
         <v>41.4</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7531,7 +7539,7 @@
         <v>84.7</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7584,7 +7592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7637,7 +7645,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7690,7 +7698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7743,7 +7751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7796,7 +7804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7849,7 +7857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7902,7 +7910,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7955,7 +7963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8008,7 +8016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8061,7 +8069,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8114,7 +8122,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8167,7 +8175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8220,7 +8228,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8273,7 +8281,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8326,7 +8334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8379,7 +8387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8432,7 +8440,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8485,7 +8493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8538,7 +8546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8591,7 +8599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8644,7 +8652,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8697,7 +8705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8750,7 +8758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8803,7 +8811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8856,7 +8864,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8909,7 +8917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8962,7 +8970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9030,7 +9038,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>